--- a/Experiment: C1/data/terminal_velocity_analysis_smaller_bead.xlsx
+++ b/Experiment: C1/data/terminal_velocity_analysis_smaller_bead.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Lab C1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3AB172F1-8792-4AC8-ADD0-A8B61589F3D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{318B4E4A-7766-4305-B780-7C369C64CE34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{317E6A58-A85F-44EB-B7BD-D5C059C4864B}"/>
   </bookViews>
@@ -60,7 +60,7 @@
     <t>Mean time /s</t>
   </si>
   <si>
-    <t>Std Dev /s</t>
+    <t>Std Error /s</t>
   </si>
 </sst>
 </file>
@@ -637,7 +637,7 @@
         <v>9.1850000000000005</v>
       </c>
       <c r="I4" s="7">
-        <v>0.79300000000000004</v>
+        <v>0.32400000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -666,7 +666,7 @@
         <v>19.163</v>
       </c>
       <c r="I5" s="10">
-        <v>1.8839999999999999</v>
+        <v>0.76900000000000002</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -695,7 +695,7 @@
         <v>29.606999999999999</v>
       </c>
       <c r="I6" s="7">
-        <v>5.4850000000000003</v>
+        <v>2.2389999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -724,7 +724,7 @@
         <v>38.884999999999998</v>
       </c>
       <c r="I7" s="10">
-        <v>6.1360000000000001</v>
+        <v>2.5049999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -753,7 +753,7 @@
         <v>48.347000000000001</v>
       </c>
       <c r="I8" s="7">
-        <v>7.64</v>
+        <v>3.1190000000000002</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -782,7 +782,7 @@
         <v>57.755000000000003</v>
       </c>
       <c r="I9" s="10">
-        <v>9.3800000000000008</v>
+        <v>3.8290000000000002</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -811,7 +811,7 @@
         <v>68.63</v>
       </c>
       <c r="I10" s="7">
-        <v>11.597</v>
+        <v>4.734</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -840,7 +840,7 @@
         <v>79.515000000000001</v>
       </c>
       <c r="I11" s="10">
-        <v>13.064</v>
+        <v>5.3330000000000002</v>
       </c>
     </row>
   </sheetData>
